--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_topology_drift_alerts.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_topology_drift_alerts.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
